--- a/backend/data/financials_by_company/1759.HK.xlsx
+++ b/backend/data/financials_by_company/1759.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,59 +672,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-307250</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7699000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-1229000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-1229000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-12363000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>11595000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1580943000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6470000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-5125000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2833000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>10956000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>13789000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-11441250</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-12363000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1655609000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>623000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>216000000</v>
       </c>
@@ -732,144 +698,98 @@
         <v>216000000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0572</v>
+        <v>0.0447</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0572</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-12363000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-12363000</v>
-      </c>
-      <c r="Y2" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>-254000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>-12363000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>5421000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-17784000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-17784000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1703000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-16081000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>6555000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-164000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>164000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>2833000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>10956000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>13789000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-21496000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>74666000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>32636000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11595000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>11595000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>623000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>53170000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1580943000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1634113000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1634113000</v>
-      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1667329.682366</v>
+        <v>3878848.052213</v>
       </c>
       <c r="C3" t="n">
-        <v>0.331873</v>
+        <v>0.373649</v>
       </c>
       <c r="D3" t="n">
-        <v>42558000</v>
+        <v>29922000</v>
       </c>
       <c r="E3" t="n">
-        <v>-5024000</v>
+        <v>10381000</v>
       </c>
       <c r="F3" t="n">
-        <v>-5024000</v>
+        <v>10381000</v>
       </c>
       <c r="G3" t="n">
-        <v>8793000</v>
+        <v>11076000</v>
       </c>
       <c r="H3" t="n">
-        <v>12333000</v>
+        <v>16104000</v>
       </c>
       <c r="I3" t="n">
-        <v>1321483000</v>
+        <v>1860651000</v>
       </c>
       <c r="J3" t="n">
-        <v>37534000</v>
+        <v>40303000</v>
       </c>
       <c r="K3" t="n">
-        <v>25201000</v>
+        <v>24199000</v>
       </c>
       <c r="L3" t="n">
-        <v>3649000</v>
+        <v>-2196000</v>
       </c>
       <c r="M3" t="n">
-        <v>15158000</v>
+        <v>14393000</v>
       </c>
       <c r="N3" t="n">
-        <v>18807000</v>
+        <v>12197000</v>
       </c>
       <c r="O3" t="n">
-        <v>12149670.317634</v>
+        <v>4573848.052213</v>
       </c>
       <c r="P3" t="n">
-        <v>8793000</v>
+        <v>11076000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1395127000</v>
+        <v>1944483000</v>
       </c>
       <c r="R3" t="n">
-        <v>695000</v>
+        <v>1853000</v>
       </c>
       <c r="S3" t="n">
         <v>216000000</v>
@@ -878,146 +798,148 @@
         <v>216000000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0407</v>
+        <v>0.0513</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0407</v>
+        <v>0.0513</v>
       </c>
       <c r="W3" t="n">
-        <v>8793000</v>
+        <v>11076000</v>
       </c>
       <c r="X3" t="n">
-        <v>8793000</v>
+        <v>11076000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>8793000</v>
+        <v>11076000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2083000</v>
+        <v>4934000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6710000</v>
+        <v>6142000</v>
       </c>
       <c r="AC3" t="n">
-        <v>6710000</v>
+        <v>6142000</v>
       </c>
       <c r="AD3" t="n">
-        <v>3333000</v>
+        <v>3664000</v>
       </c>
       <c r="AE3" t="n">
-        <v>10043000</v>
+        <v>9806000</v>
       </c>
       <c r="AF3" t="n">
-        <v>4092000</v>
+        <v>5985000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-6023000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>2364000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-2364000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>564000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6023000</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>3649000</v>
+        <v>-2196000</v>
       </c>
       <c r="AM3" t="n">
-        <v>15158000</v>
+        <v>14393000</v>
       </c>
       <c r="AN3" t="n">
-        <v>18807000</v>
+        <v>12197000</v>
       </c>
       <c r="AO3" t="n">
-        <v>10985000</v>
+        <v>3463000</v>
       </c>
       <c r="AP3" t="n">
-        <v>73644000</v>
+        <v>83832000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>30748000</v>
+        <v>33070000</v>
       </c>
       <c r="AR3" t="n">
-        <v>12333000</v>
+        <v>16104000</v>
       </c>
       <c r="AS3" t="n">
-        <v>12333000</v>
+        <v>16104000</v>
       </c>
       <c r="AT3" t="n">
-        <v>695000</v>
+        <v>1853000</v>
       </c>
       <c r="AU3" t="n">
-        <v>84629000</v>
+        <v>87295000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1321483000</v>
+        <v>1860651000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1406112000</v>
+        <v>1947946000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1406112000</v>
+        <v>1947946000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>3878848.052213</v>
+        <v>-1667329.682366</v>
       </c>
       <c r="C4" t="n">
-        <v>0.373649</v>
+        <v>0.331873</v>
       </c>
       <c r="D4" t="n">
-        <v>29922000</v>
+        <v>42558000</v>
       </c>
       <c r="E4" t="n">
-        <v>10381000</v>
+        <v>-5024000</v>
       </c>
       <c r="F4" t="n">
-        <v>10381000</v>
+        <v>-5024000</v>
       </c>
       <c r="G4" t="n">
-        <v>11076000</v>
+        <v>8793000</v>
       </c>
       <c r="H4" t="n">
-        <v>16104000</v>
+        <v>12333000</v>
       </c>
       <c r="I4" t="n">
-        <v>1860651000</v>
+        <v>1321483000</v>
       </c>
       <c r="J4" t="n">
-        <v>40303000</v>
+        <v>37534000</v>
       </c>
       <c r="K4" t="n">
-        <v>24199000</v>
+        <v>25201000</v>
       </c>
       <c r="L4" t="n">
-        <v>-2196000</v>
+        <v>3649000</v>
       </c>
       <c r="M4" t="n">
-        <v>14393000</v>
+        <v>15158000</v>
       </c>
       <c r="N4" t="n">
-        <v>12197000</v>
+        <v>18807000</v>
       </c>
       <c r="O4" t="n">
-        <v>4573848.052213</v>
+        <v>12149670.317634</v>
       </c>
       <c r="P4" t="n">
-        <v>11076000</v>
+        <v>8793000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1944483000</v>
+        <v>1395127000</v>
       </c>
       <c r="R4" t="n">
-        <v>1853000</v>
+        <v>695000</v>
       </c>
       <c r="S4" t="n">
         <v>216000000</v>
@@ -1026,148 +948,146 @@
         <v>216000000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0513</v>
+        <v>0.0407</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0513</v>
+        <v>0.0407</v>
       </c>
       <c r="W4" t="n">
-        <v>11076000</v>
+        <v>8793000</v>
       </c>
       <c r="X4" t="n">
-        <v>11076000</v>
+        <v>8793000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>11076000</v>
+        <v>8793000</v>
       </c>
       <c r="AA4" t="n">
-        <v>4934000</v>
+        <v>2083000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6142000</v>
+        <v>6710000</v>
       </c>
       <c r="AC4" t="n">
-        <v>6142000</v>
+        <v>6710000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3664000</v>
+        <v>3333000</v>
       </c>
       <c r="AE4" t="n">
-        <v>9806000</v>
+        <v>10043000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5985000</v>
+        <v>4092000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2364000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-2364000</v>
-      </c>
+        <v>-6023000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>564000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>6023000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-2196000</v>
+        <v>3649000</v>
       </c>
       <c r="AM4" t="n">
-        <v>14393000</v>
+        <v>15158000</v>
       </c>
       <c r="AN4" t="n">
-        <v>12197000</v>
+        <v>18807000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3463000</v>
+        <v>10985000</v>
       </c>
       <c r="AP4" t="n">
-        <v>83832000</v>
+        <v>73644000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>33070000</v>
+        <v>30748000</v>
       </c>
       <c r="AR4" t="n">
-        <v>16104000</v>
+        <v>12333000</v>
       </c>
       <c r="AS4" t="n">
-        <v>16104000</v>
+        <v>12333000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1853000</v>
+        <v>695000</v>
       </c>
       <c r="AU4" t="n">
-        <v>87295000</v>
+        <v>84629000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1860651000</v>
+        <v>1321483000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1947946000</v>
+        <v>1406112000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1947946000</v>
+        <v>1406112000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-741298.590346</v>
+        <v>-317750</v>
       </c>
       <c r="C5" t="n">
-        <v>0.398548</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>59606000</v>
+        <v>7741000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1860000</v>
+        <v>-1271000</v>
       </c>
       <c r="F5" t="n">
-        <v>-1860000</v>
+        <v>-1271000</v>
       </c>
       <c r="G5" t="n">
-        <v>9664000</v>
+        <v>-12363000</v>
       </c>
       <c r="H5" t="n">
-        <v>23649000</v>
+        <v>11595000</v>
       </c>
       <c r="I5" t="n">
-        <v>1815035000</v>
+        <v>1580943000</v>
       </c>
       <c r="J5" t="n">
-        <v>57746000</v>
+        <v>6470000</v>
       </c>
       <c r="K5" t="n">
-        <v>34097000</v>
+        <v>-5125000</v>
       </c>
       <c r="L5" t="n">
-        <v>-3555000</v>
+        <v>2833000</v>
       </c>
       <c r="M5" t="n">
-        <v>20051000</v>
+        <v>10956000</v>
       </c>
       <c r="N5" t="n">
-        <v>16496000</v>
+        <v>13789000</v>
       </c>
       <c r="O5" t="n">
-        <v>10782701.409654</v>
+        <v>-11409750</v>
       </c>
       <c r="P5" t="n">
-        <v>9664000</v>
+        <v>-12363000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1911896000</v>
+        <v>1655567000</v>
       </c>
       <c r="R5" t="n">
-        <v>2069000</v>
+        <v>623000</v>
       </c>
       <c r="S5" t="n">
         <v>216000000</v>
@@ -1176,90 +1096,234 @@
         <v>216000000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0447</v>
+        <v>-0.0572</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0447</v>
+        <v>-0.0572</v>
       </c>
       <c r="W5" t="n">
-        <v>9664000</v>
+        <v>-12363000</v>
       </c>
       <c r="X5" t="n">
-        <v>9664000</v>
+        <v>-12363000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>9664000</v>
+        <v>-12363000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1216000</v>
+        <v>5421000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8448000</v>
+        <v>-17784000</v>
       </c>
       <c r="AC5" t="n">
-        <v>8448000</v>
+        <v>-17784000</v>
       </c>
       <c r="AD5" t="n">
-        <v>5598000</v>
+        <v>1703000</v>
       </c>
       <c r="AE5" t="n">
-        <v>14046000</v>
+        <v>-16081000</v>
       </c>
       <c r="AF5" t="n">
-        <v>24418000</v>
+        <v>6555000</v>
       </c>
       <c r="AG5" t="n">
-        <v>254000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-254000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-206000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>164000</v>
+      </c>
       <c r="AK5" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2833000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>10956000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13789000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-21454000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>74624000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>32636000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11595000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>11595000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>623000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>53170000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1580943000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1634113000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1634113000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-4808250</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-19233000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-19233000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-26058000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13428000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2152384000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-6533000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-19961000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3964000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>13908000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>17872000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-11633250</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-26058000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2214212000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1447000</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>-26058000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-26058000</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="AL5" t="n">
-        <v>-3555000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>20051000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>16496000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-4074000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>96861000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>35129000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>23649000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>23649000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2069000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>92787000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1815035000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1907822000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1907822000</v>
+      <c r="Z6" t="n">
+        <v>-26058000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9317000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-35375000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-35375000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1506000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-33869000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4057000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-19586000</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>4353000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>15188000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3964000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>13908000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>17872000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-22584000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>61828000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>18163000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13428000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>13428000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1447000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>39244000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2152384000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2191628000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2191628000</v>
       </c>
     </row>
   </sheetData>
@@ -1273,7 +1337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL5"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,199 +1659,77 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>216000000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>216000000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>565560000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>722282000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>356947000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1092874000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>228371000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>356947000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2282000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>372874000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>372874000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>388277000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>15403000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>372874000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>154956000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>173360000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1892000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1892000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>751334000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3076000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1671000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1405000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1405000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>748258000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>720877000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>877000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>720000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9516000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2109000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>81000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>7326000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1139611000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>162982000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>10341000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>24301000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24301000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>23847000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>8922000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>14925000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>15927000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>15927000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>88566000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-177676000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>266242000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>20786000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>110515000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>66003000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>68938000</v>
-      </c>
-      <c r="AX2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
         <v>0</v>
       </c>
-      <c r="AY2" t="n">
-        <v>976629000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="n">
-        <v>615000000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>19984000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3059000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3059000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>23483000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>158063000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>-3825000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>161888000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>154440000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>154440000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>154440000</v>
-      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>216000000</v>
@@ -1796,43 +1738,43 @@
         <v>216000000</v>
       </c>
       <c r="D3" t="n">
-        <v>349628000</v>
+        <v>415667000</v>
       </c>
       <c r="E3" t="n">
-        <v>510946000</v>
+        <v>511561000</v>
       </c>
       <c r="F3" t="n">
-        <v>369478000</v>
+        <v>358409000</v>
       </c>
       <c r="G3" t="n">
-        <v>893708000</v>
+        <v>883363000</v>
       </c>
       <c r="H3" t="n">
-        <v>224373000</v>
+        <v>193222000</v>
       </c>
       <c r="I3" t="n">
-        <v>369478000</v>
+        <v>358409000</v>
       </c>
       <c r="J3" t="n">
-        <v>3446000</v>
+        <v>4061000</v>
       </c>
       <c r="K3" t="n">
-        <v>386208000</v>
+        <v>375863000</v>
       </c>
       <c r="L3" t="n">
-        <v>386208000</v>
+        <v>375863000</v>
       </c>
       <c r="M3" t="n">
-        <v>407032000</v>
+        <v>398770000</v>
       </c>
       <c r="N3" t="n">
-        <v>20824000</v>
+        <v>22907000</v>
       </c>
       <c r="O3" t="n">
-        <v>386208000</v>
+        <v>375863000</v>
       </c>
       <c r="P3" t="n">
-        <v>167525000</v>
+        <v>163420000</v>
       </c>
       <c r="Q3" t="n">
         <v>173360000</v>
@@ -1844,142 +1786,142 @@
         <v>1892000</v>
       </c>
       <c r="T3" t="n">
-        <v>548860000</v>
+        <v>549148000</v>
       </c>
       <c r="U3" t="n">
-        <v>4132000</v>
+        <v>4724000</v>
       </c>
       <c r="V3" t="n">
-        <v>1736000</v>
+        <v>1838000</v>
       </c>
       <c r="W3" t="n">
-        <v>2396000</v>
+        <v>2886000</v>
       </c>
       <c r="X3" t="n">
-        <v>2396000</v>
+        <v>2886000</v>
       </c>
       <c r="Y3" t="n">
-        <v>544728000</v>
+        <v>544424000</v>
       </c>
       <c r="Z3" t="n">
-        <v>508550000</v>
+        <v>508675000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1050000</v>
+        <v>1175000</v>
       </c>
       <c r="AB3" t="n">
         <v>507500000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3684000</v>
+        <v>12692000</v>
       </c>
       <c r="AD3" t="n">
-        <v>2281000</v>
+        <v>2775000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1161000</v>
+        <v>3054000</v>
       </c>
       <c r="AF3" t="n">
-        <v>242000</v>
+        <v>6863000</v>
       </c>
       <c r="AG3" t="n">
-        <v>955892000</v>
+        <v>947918000</v>
       </c>
       <c r="AH3" t="n">
-        <v>186791000</v>
+        <v>210272000</v>
       </c>
       <c r="AI3" t="n">
-        <v>10909000</v>
+        <v>11676000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25366000</v>
+        <v>24367000</v>
       </c>
       <c r="AK3" t="n">
-        <v>25366000</v>
+        <v>24367000</v>
       </c>
       <c r="AL3" t="n">
-        <v>27886000</v>
+        <v>32501000</v>
       </c>
       <c r="AM3" t="n">
-        <v>10640000</v>
+        <v>12347000</v>
       </c>
       <c r="AN3" t="n">
-        <v>17246000</v>
+        <v>20154000</v>
       </c>
       <c r="AO3" t="n">
-        <v>16730000</v>
+        <v>17454000</v>
       </c>
       <c r="AP3" t="n">
-        <v>16730000</v>
+        <v>17454000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>105900000</v>
+        <v>124274000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-171056000</v>
+        <v>-156483000</v>
       </c>
       <c r="AS3" t="n">
-        <v>276956000</v>
+        <v>280757000</v>
       </c>
       <c r="AT3" t="n">
-        <v>34398000</v>
+        <v>36410000</v>
       </c>
       <c r="AU3" t="n">
-        <v>108801000</v>
+        <v>108759000</v>
       </c>
       <c r="AV3" t="n">
-        <v>67530000</v>
+        <v>69533000</v>
       </c>
       <c r="AW3" t="n">
-        <v>66227000</v>
+        <v>66055000</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>769101000</v>
+        <v>737646000</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>387500000</v>
+        <v>427500000</v>
       </c>
       <c r="BB3" t="n">
-        <v>31810000</v>
+        <v>63871000</v>
       </c>
       <c r="BC3" t="n">
-        <v>2577000</v>
+        <v>2097000</v>
       </c>
       <c r="BD3" t="n">
-        <v>2577000</v>
+        <v>2097000</v>
       </c>
       <c r="BE3" t="n">
-        <v>11422000</v>
+        <v>62059000</v>
       </c>
       <c r="BF3" t="n">
-        <v>1255000</v>
+        <v>5044000</v>
       </c>
       <c r="BG3" t="n">
-        <v>176665000</v>
+        <v>211172000</v>
       </c>
       <c r="BH3" t="n">
-        <v>-2410000</v>
+        <v>-1846000</v>
       </c>
       <c r="BI3" t="n">
-        <v>179075000</v>
+        <v>150959000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>157872000</v>
+        <v>91833000</v>
       </c>
       <c r="BK3" t="n">
-        <v>157872000</v>
+        <v>91833000</v>
       </c>
       <c r="BL3" t="n">
-        <v>157872000</v>
+        <v>91833000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>216000000</v>
@@ -1988,43 +1930,43 @@
         <v>216000000</v>
       </c>
       <c r="D4" t="n">
-        <v>415667000</v>
+        <v>349628000</v>
       </c>
       <c r="E4" t="n">
-        <v>511561000</v>
+        <v>510946000</v>
       </c>
       <c r="F4" t="n">
-        <v>358409000</v>
+        <v>369478000</v>
       </c>
       <c r="G4" t="n">
-        <v>883363000</v>
+        <v>893708000</v>
       </c>
       <c r="H4" t="n">
-        <v>193222000</v>
+        <v>224373000</v>
       </c>
       <c r="I4" t="n">
-        <v>358409000</v>
+        <v>369478000</v>
       </c>
       <c r="J4" t="n">
-        <v>4061000</v>
+        <v>3446000</v>
       </c>
       <c r="K4" t="n">
-        <v>375863000</v>
+        <v>386208000</v>
       </c>
       <c r="L4" t="n">
-        <v>375863000</v>
+        <v>386208000</v>
       </c>
       <c r="M4" t="n">
-        <v>398770000</v>
+        <v>407032000</v>
       </c>
       <c r="N4" t="n">
-        <v>22907000</v>
+        <v>20824000</v>
       </c>
       <c r="O4" t="n">
-        <v>375863000</v>
+        <v>386208000</v>
       </c>
       <c r="P4" t="n">
-        <v>163420000</v>
+        <v>167525000</v>
       </c>
       <c r="Q4" t="n">
         <v>173360000</v>
@@ -2036,142 +1978,142 @@
         <v>1892000</v>
       </c>
       <c r="T4" t="n">
-        <v>549148000</v>
+        <v>548860000</v>
       </c>
       <c r="U4" t="n">
-        <v>4724000</v>
+        <v>4132000</v>
       </c>
       <c r="V4" t="n">
-        <v>1838000</v>
+        <v>1736000</v>
       </c>
       <c r="W4" t="n">
-        <v>2886000</v>
+        <v>2396000</v>
       </c>
       <c r="X4" t="n">
-        <v>2886000</v>
+        <v>2396000</v>
       </c>
       <c r="Y4" t="n">
-        <v>544424000</v>
+        <v>544728000</v>
       </c>
       <c r="Z4" t="n">
-        <v>508675000</v>
+        <v>508550000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1175000</v>
+        <v>1050000</v>
       </c>
       <c r="AB4" t="n">
         <v>507500000</v>
       </c>
       <c r="AC4" t="n">
-        <v>12692000</v>
+        <v>3684000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2775000</v>
+        <v>2281000</v>
       </c>
       <c r="AE4" t="n">
-        <v>3054000</v>
+        <v>1161000</v>
       </c>
       <c r="AF4" t="n">
-        <v>6863000</v>
+        <v>242000</v>
       </c>
       <c r="AG4" t="n">
-        <v>947918000</v>
+        <v>955892000</v>
       </c>
       <c r="AH4" t="n">
-        <v>210272000</v>
+        <v>186791000</v>
       </c>
       <c r="AI4" t="n">
-        <v>11676000</v>
+        <v>10909000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24367000</v>
+        <v>25366000</v>
       </c>
       <c r="AK4" t="n">
-        <v>24367000</v>
+        <v>25366000</v>
       </c>
       <c r="AL4" t="n">
-        <v>32501000</v>
+        <v>27886000</v>
       </c>
       <c r="AM4" t="n">
-        <v>12347000</v>
+        <v>10640000</v>
       </c>
       <c r="AN4" t="n">
-        <v>20154000</v>
+        <v>17246000</v>
       </c>
       <c r="AO4" t="n">
-        <v>17454000</v>
+        <v>16730000</v>
       </c>
       <c r="AP4" t="n">
-        <v>17454000</v>
+        <v>16730000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>124274000</v>
+        <v>105900000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-156483000</v>
+        <v>-171056000</v>
       </c>
       <c r="AS4" t="n">
-        <v>280757000</v>
+        <v>276956000</v>
       </c>
       <c r="AT4" t="n">
-        <v>36410000</v>
+        <v>34398000</v>
       </c>
       <c r="AU4" t="n">
-        <v>108759000</v>
+        <v>108801000</v>
       </c>
       <c r="AV4" t="n">
-        <v>69533000</v>
+        <v>67530000</v>
       </c>
       <c r="AW4" t="n">
-        <v>66055000</v>
+        <v>66227000</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>737646000</v>
+        <v>769101000</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>427500000</v>
+        <v>387500000</v>
       </c>
       <c r="BB4" t="n">
-        <v>63871000</v>
+        <v>31810000</v>
       </c>
       <c r="BC4" t="n">
-        <v>2097000</v>
+        <v>2577000</v>
       </c>
       <c r="BD4" t="n">
-        <v>2097000</v>
+        <v>2577000</v>
       </c>
       <c r="BE4" t="n">
-        <v>62059000</v>
+        <v>11422000</v>
       </c>
       <c r="BF4" t="n">
-        <v>5044000</v>
+        <v>1255000</v>
       </c>
       <c r="BG4" t="n">
-        <v>211172000</v>
+        <v>176665000</v>
       </c>
       <c r="BH4" t="n">
-        <v>-1846000</v>
+        <v>-2410000</v>
       </c>
       <c r="BI4" t="n">
-        <v>150959000</v>
+        <v>179075000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>91833000</v>
+        <v>157872000</v>
       </c>
       <c r="BK4" t="n">
-        <v>91833000</v>
+        <v>157872000</v>
       </c>
       <c r="BL4" t="n">
-        <v>91833000</v>
+        <v>157872000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>216000000</v>
@@ -2180,43 +2122,43 @@
         <v>216000000</v>
       </c>
       <c r="D5" t="n">
-        <v>399050000</v>
+        <v>565560000</v>
       </c>
       <c r="E5" t="n">
-        <v>508365000</v>
+        <v>722282000</v>
       </c>
       <c r="F5" t="n">
-        <v>338420000</v>
+        <v>356947000</v>
       </c>
       <c r="G5" t="n">
-        <v>833097000</v>
+        <v>1092874000</v>
       </c>
       <c r="H5" t="n">
-        <v>166530000</v>
+        <v>228371000</v>
       </c>
       <c r="I5" t="n">
-        <v>338420000</v>
+        <v>356947000</v>
       </c>
       <c r="J5" t="n">
-        <v>31865000</v>
+        <v>2282000</v>
       </c>
       <c r="K5" t="n">
-        <v>356597000</v>
+        <v>372874000</v>
       </c>
       <c r="L5" t="n">
-        <v>356597000</v>
+        <v>372874000</v>
       </c>
       <c r="M5" t="n">
-        <v>384438000</v>
+        <v>388277000</v>
       </c>
       <c r="N5" t="n">
-        <v>27841000</v>
+        <v>15403000</v>
       </c>
       <c r="O5" t="n">
-        <v>356597000</v>
+        <v>372874000</v>
       </c>
       <c r="P5" t="n">
-        <v>155343000</v>
+        <v>154956000</v>
       </c>
       <c r="Q5" t="n">
         <v>173360000</v>
@@ -2228,139 +2170,329 @@
         <v>1892000</v>
       </c>
       <c r="T5" t="n">
-        <v>535029000</v>
+        <v>751334000</v>
       </c>
       <c r="U5" t="n">
-        <v>30361000</v>
+        <v>3076000</v>
       </c>
       <c r="V5" t="n">
-        <v>1809000</v>
+        <v>1671000</v>
       </c>
       <c r="W5" t="n">
-        <v>28552000</v>
+        <v>1405000</v>
       </c>
       <c r="X5" t="n">
-        <v>28552000</v>
+        <v>1405000</v>
       </c>
       <c r="Y5" t="n">
-        <v>504668000</v>
+        <v>748258000</v>
       </c>
       <c r="Z5" t="n">
-        <v>479813000</v>
+        <v>720877000</v>
       </c>
       <c r="AA5" t="n">
-        <v>3313000</v>
+        <v>877000</v>
       </c>
       <c r="AB5" t="n">
-        <v>476500000</v>
+        <v>720000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>9530000</v>
+        <v>9516000</v>
       </c>
       <c r="AD5" t="n">
-        <v>6109000</v>
+        <v>2109000</v>
       </c>
       <c r="AE5" t="n">
-        <v>698000</v>
+        <v>81000</v>
       </c>
       <c r="AF5" t="n">
-        <v>2723000</v>
+        <v>7326000</v>
       </c>
       <c r="AG5" t="n">
-        <v>919467000</v>
+        <v>1139611000</v>
       </c>
       <c r="AH5" t="n">
-        <v>248269000</v>
+        <v>162982000</v>
       </c>
       <c r="AI5" t="n">
-        <v>11384000</v>
+        <v>10341000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16350000</v>
+        <v>24301000</v>
       </c>
       <c r="AK5" t="n">
-        <v>16350000</v>
+        <v>24301000</v>
       </c>
       <c r="AL5" t="n">
-        <v>33648000</v>
+        <v>23847000</v>
       </c>
       <c r="AM5" t="n">
-        <v>13488000</v>
+        <v>8922000</v>
       </c>
       <c r="AN5" t="n">
-        <v>20160000</v>
+        <v>14925000</v>
       </c>
       <c r="AO5" t="n">
-        <v>18177000</v>
+        <v>15927000</v>
       </c>
       <c r="AP5" t="n">
-        <v>18177000</v>
+        <v>15927000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>168710000</v>
+        <v>88566000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-169614000</v>
+        <v>-177676000</v>
       </c>
       <c r="AS5" t="n">
-        <v>338324000</v>
+        <v>266242000</v>
       </c>
       <c r="AT5" t="n">
-        <v>38690000</v>
+        <v>20786000</v>
       </c>
       <c r="AU5" t="n">
-        <v>162766000</v>
+        <v>110515000</v>
       </c>
       <c r="AV5" t="n">
-        <v>68580000</v>
+        <v>66003000</v>
       </c>
       <c r="AW5" t="n">
-        <v>68288000</v>
+        <v>68938000</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>671198000</v>
-      </c>
-      <c r="AZ5" t="n">
+        <v>976629000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>615000000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>19984000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3059000</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3059000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>23483000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>158063000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-3825000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>161888000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>154440000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>154440000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>154440000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>216000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>216000000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1555551000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1680977000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>330076000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2024028000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>222278000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>330076000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1977000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>345028000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>345028000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>351401000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6373000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>345028000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>128438000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>173360000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1892000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1892000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1718885000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3256000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2007000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1249000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1249000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1715629000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1679728000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>728000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1679000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13737000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1997000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>227000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11513000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2070286000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>132379000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>9659000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>24654000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>24654000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>20162000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>8870000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>11292000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>14952000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>14952000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>62952000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-178728000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>241680000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8179000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>112712000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>47700000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>73089000</v>
+      </c>
+      <c r="AX6" t="n">
         <v>0</v>
       </c>
-      <c r="BA5" t="n">
-        <v>394500000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>50405000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2937000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2937000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>23357000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>11108000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>111441000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>-1846000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>113287000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>77450000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>77450000</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>77450000</v>
+      <c r="AY6" t="n">
+        <v>1937907000</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>1635000000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>37380000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2479000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2479000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>20251000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3040000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>116308000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-484000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>116792000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>123449000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>123449000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>123449000</v>
       </c>
     </row>
   </sheetData>
@@ -2374,7 +2506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP5"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,475 +2715,573 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Sale Of Business</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Provisionand Write Offof Assets</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Gain Loss On Sale Of Business</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2443000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1187500000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1400000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-2739000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>154440000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>157872000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-971000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-2461000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-26921000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-227500000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-10956000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>212500000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>212500000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-1187500000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1400000000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>19278000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>18218000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2320000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>-2410000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>329000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-2739000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>5182000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-2545000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2094000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-8797000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-482000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>11373000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-2849000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>11595000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>11595000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1065000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>8605000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-16081000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>279903000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-196597000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>476500000</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>102888000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>102888000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-20702000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-20702000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>12958000</v>
+        <v>893000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1442500000</v>
+        <v>-476500000</v>
       </c>
       <c r="D3" t="n">
-        <v>1442500000</v>
+        <v>507500000</v>
       </c>
       <c r="E3" t="n">
-        <v>-1802000</v>
+        <v>-4877000</v>
       </c>
       <c r="F3" t="n">
-        <v>157872000</v>
+        <v>91833000</v>
       </c>
       <c r="G3" t="n">
-        <v>91833000</v>
+        <v>77450000</v>
       </c>
       <c r="H3" t="n">
-        <v>1552000</v>
+        <v>8190000</v>
       </c>
       <c r="I3" t="n">
-        <v>64487000</v>
+        <v>6193000</v>
       </c>
       <c r="J3" t="n">
-        <v>23009000</v>
+        <v>-19564000</v>
       </c>
       <c r="K3" t="n">
-        <v>40000000</v>
+        <v>-33000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-15158000</v>
+        <v>-14393000</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>31000000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>31000000</v>
       </c>
       <c r="O3" t="n">
-        <v>-1442500000</v>
+        <v>-476500000</v>
       </c>
       <c r="P3" t="n">
-        <v>1442500000</v>
+        <v>507500000</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>26718000</v>
+        <v>19987000</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>22516000</v>
+        <v>17086000</v>
       </c>
       <c r="W3" t="n">
-        <v>2320000</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="n">
-        <v>-18000</v>
+        <v>801000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1784000</v>
+        <v>5678000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1802000</v>
+        <v>-4877000</v>
       </c>
       <c r="AE3" t="n">
-        <v>14760000</v>
+        <v>5770000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1121000</v>
+        <v>-4817000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-15669000</v>
+        <v>-14270000</v>
       </c>
       <c r="AH3" t="n">
-        <v>429000</v>
+        <v>10894000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-480000</v>
+        <v>840000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-15618000</v>
+        <v>-26004000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2929000</v>
+        <v>-168000</v>
       </c>
       <c r="AL3" t="n">
-        <v>12333000</v>
+        <v>16104000</v>
       </c>
       <c r="AM3" t="n">
-        <v>12333000</v>
+        <v>16104000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-999000</v>
+        <v>-8017000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1978000</v>
+        <v>5985000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10043000</v>
-      </c>
+        <v>9806000</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>893000</v>
+        <v>12958000</v>
       </c>
       <c r="C4" t="n">
-        <v>-476500000</v>
+        <v>-1442500000</v>
       </c>
       <c r="D4" t="n">
-        <v>507500000</v>
+        <v>1442500000</v>
       </c>
       <c r="E4" t="n">
-        <v>-4877000</v>
+        <v>-1802000</v>
       </c>
       <c r="F4" t="n">
+        <v>157872000</v>
+      </c>
+      <c r="G4" t="n">
         <v>91833000</v>
       </c>
-      <c r="G4" t="n">
-        <v>77450000</v>
-      </c>
       <c r="H4" t="n">
-        <v>8190000</v>
+        <v>1552000</v>
       </c>
       <c r="I4" t="n">
-        <v>6193000</v>
+        <v>64487000</v>
       </c>
       <c r="J4" t="n">
-        <v>-19564000</v>
+        <v>23009000</v>
       </c>
       <c r="K4" t="n">
-        <v>-33000000</v>
+        <v>40000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-14393000</v>
+        <v>-15158000</v>
       </c>
       <c r="M4" t="n">
-        <v>31000000</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>31000000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-476500000</v>
+        <v>-1442500000</v>
       </c>
       <c r="P4" t="n">
-        <v>507500000</v>
+        <v>1442500000</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>19987000</v>
+        <v>26718000</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>17086000</v>
+        <v>22516000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>2320000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>801000</v>
+        <v>-18000</v>
       </c>
       <c r="AC4" t="n">
-        <v>5678000</v>
+        <v>1784000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-4877000</v>
+        <v>-1802000</v>
       </c>
       <c r="AE4" t="n">
-        <v>5770000</v>
+        <v>14760000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-4817000</v>
+        <v>1121000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-14270000</v>
+        <v>-15669000</v>
       </c>
       <c r="AH4" t="n">
-        <v>10894000</v>
+        <v>429000</v>
       </c>
       <c r="AI4" t="n">
-        <v>840000</v>
+        <v>-480000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-26004000</v>
+        <v>-15618000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-168000</v>
+        <v>-2929000</v>
       </c>
       <c r="AL4" t="n">
-        <v>16104000</v>
+        <v>12333000</v>
       </c>
       <c r="AM4" t="n">
-        <v>16104000</v>
+        <v>12333000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-8017000</v>
+        <v>-999000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5985000</v>
+        <v>1978000</v>
       </c>
       <c r="AP4" t="n">
-        <v>9806000</v>
-      </c>
+        <v>10043000</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>17575000</v>
+        <v>2443000</v>
       </c>
       <c r="C5" t="n">
-        <v>-196597000</v>
+        <v>-1187500000</v>
       </c>
       <c r="D5" t="n">
-        <v>476500000</v>
+        <v>1400000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-3715000</v>
+        <v>-2739000</v>
       </c>
       <c r="F5" t="n">
-        <v>77450000</v>
+        <v>154440000</v>
       </c>
       <c r="G5" t="n">
-        <v>56304000</v>
+        <v>157872000</v>
       </c>
       <c r="H5" t="n">
-        <v>-3262000</v>
+        <v>-971000</v>
       </c>
       <c r="I5" t="n">
-        <v>24408000</v>
+        <v>-2461000</v>
       </c>
       <c r="J5" t="n">
-        <v>-87204000</v>
+        <v>-26921000</v>
       </c>
       <c r="K5" t="n">
-        <v>-341160000</v>
+        <v>-227500000</v>
       </c>
       <c r="L5" t="n">
-        <v>-20051000</v>
+        <v>-10956000</v>
       </c>
       <c r="M5" t="n">
-        <v>279903000</v>
+        <v>212500000</v>
       </c>
       <c r="N5" t="n">
-        <v>279903000</v>
+        <v>212500000</v>
       </c>
       <c r="O5" t="n">
-        <v>-196597000</v>
+        <v>-1187500000</v>
       </c>
       <c r="P5" t="n">
-        <v>476500000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>279903000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-196597000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>476500000</v>
-      </c>
+        <v>1400000000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>90322000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>70000000</v>
-      </c>
+        <v>19278000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>4696000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="n">
-        <v>102888000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>102888000</v>
-      </c>
+        <v>18218000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2320000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-20702000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-20702000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1560000</v>
+        <v>-2410000</v>
       </c>
       <c r="AC5" t="n">
-        <v>2155000</v>
+        <v>329000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3715000</v>
+        <v>-2739000</v>
       </c>
       <c r="AE5" t="n">
-        <v>21290000</v>
+        <v>5182000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-7753000</v>
+        <v>-2545000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1403000</v>
+        <v>2094000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1400000</v>
+        <v>-8797000</v>
       </c>
       <c r="AI5" t="n">
-        <v>294000</v>
+        <v>-482000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-297000</v>
+        <v>11373000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-14570000</v>
+        <v>-2849000</v>
       </c>
       <c r="AL5" t="n">
-        <v>23649000</v>
+        <v>11595000</v>
       </c>
       <c r="AM5" t="n">
-        <v>23649000</v>
+        <v>11595000</v>
       </c>
       <c r="AN5" t="n">
-        <v>2114000</v>
+        <v>1065000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-254000</v>
+        <v>8605000</v>
       </c>
       <c r="AP5" t="n">
-        <v>14046000</v>
+        <v>-16081000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>30043000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1505000000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2464000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-3081000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>123449000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>154440000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1788000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-29203000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-75835000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1020000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-13908000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>959000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>959000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1505000000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2464000000</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>13508000</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>12184000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>253000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-808000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-3081000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-3081000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>33124000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-925000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>42063000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>8526000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>580000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>32957000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-3456000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>13428000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>13428000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-353000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>982000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-33869000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1061000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4353000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-597000</v>
       </c>
     </row>
   </sheetData>
@@ -3566,187 +3796,187 @@
       </c>
       <c r="CV1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EG1" t="inlineStr">
@@ -3823,7 +4053,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Sino Gas Holdings Group Limited, together with its subsidiaries, engages in the retail and wholesale of liquefied petroleum gas (LPG), compressed natural gas (CNG), and liquefied natural gas (LNG) in the People's Republic of China. The company is involved fuel transportation activities; and sale of CNG, LPG, and LNG to vehicular end-users by operating gas refueling stations. It serves industrial customers and gas merchants. Sino Gas Holdings Group Limited was incorporated in 2018 and is headquartered in Guangzhou, China. Sino Gas Holdings Group Limited is a subsidiary of China Full Limited.</t>
+          <t>Sino Gas Holdings Group Limited, together with its subsidiaries, engages in the retail and wholesale of liquefied petroleum gas (LPG), compressed natural gas (CNG), and liquefied natural gas (LNG) in the People's Republic of China. The company is involved fuel transportation activities; and sale of CNG, LPG, and LNG to vehicular end-users by operating gas refueling stations. It serves industrial customers and gas merchants. The company was incorporated in 2018 and is headquartered in Guangzhou, China. Sino Gas Holdings Group Limited is a subsidiary of China Full Limited.</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3831,7 +4061,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Guang  Ji', 'age': 62, 'title': 'Executive Chairman of the Board', 'yearBorn': 1963, 'fiscalYear': 2025, 'totalPay': 1233740, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ling  Ji', 'age': 35, 'title': 'Executive Vice Chairman, CEO &amp; Financial Controller', 'yearBorn': 1990, 'fiscalYear': 2025, 'totalPay': 630192, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Feng  Zhou', 'age': 41, 'title': 'Executive Director', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 483070, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Pei  Li', 'age': 55, 'title': 'GM (In respect of business in Henan Province) &amp; Executive VP', 'yearBorn': 1970, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wai Ki  Lai', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Guang  Ji', 'age': 62, 'title': 'Executive Chairman of the Board', 'yearBorn': 1963, 'fiscalYear': 2025, 'totalPay': 1233546, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ling  Ji', 'age': 35, 'title': 'Executive Vice Chairman, CEO &amp; Financial Controller', 'yearBorn': 1990, 'fiscalYear': 2025, 'totalPay': 630093, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Feng  Zhou', 'age': 41, 'title': 'Executive Director', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 482994, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Pei  Li', 'age': 55, 'title': 'GM (In respect of business in Henan Province) &amp; Executive VP', 'yearBorn': 1970, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wai Ki  Lai', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3849,55 +4079,55 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.99</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="X2" t="n">
-        <v>0.99</v>
+        <v>0.62</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.99</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.99</v>
+        <v>0.62</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.148</v>
+        <v>0.192</v>
       </c>
       <c r="AE2" t="n">
-        <v>12000</v>
+        <v>138000</v>
       </c>
       <c r="AF2" t="n">
-        <v>12000</v>
+        <v>138000</v>
       </c>
       <c r="AG2" t="n">
-        <v>9733</v>
+        <v>122100</v>
       </c>
       <c r="AH2" t="n">
-        <v>9000</v>
+        <v>658700</v>
       </c>
       <c r="AI2" t="n">
-        <v>9000</v>
+        <v>658700</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -3906,16 +4136,16 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>211680000</v>
+        <v>127439992</v>
       </c>
       <c r="AO2" t="n">
-        <v>213840000</v>
+        <v>127440000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AR2" t="n">
         <v>4.9</v>
@@ -3924,13 +4154,13 @@
         <v>0.27</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.09658573600000001</v>
+        <v>0.05814855</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.9356</v>
+        <v>0.8582</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01915</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -3947,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>1755330048</v>
+        <v>1664610048</v>
       </c>
       <c r="BB2" t="n">
         <v>-0.01189</v>
@@ -3968,10 +4198,10 @@
         <v>216000000</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.8495524</v>
+        <v>1.8463538</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.52985793</v>
+        <v>0.31954873</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
@@ -3989,16 +4219,16 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.801</v>
+        <v>0.76</v>
       </c>
       <c r="BP2" t="n">
-        <v>-140.381</v>
+        <v>-133.126</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27272725</v>
+        <v>-0.7050000400000001</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27449715</v>
+        <v>0.2568333</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -4006,7 +4236,7 @@
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -4107,138 +4337,138 @@
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>SINO GAS HLDGS</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CX2" t="n">
+        <v>1781769253</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>finmb_279073844</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DA2" t="n">
+      <c r="DC2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DC2" t="b">
+      <c r="DE2" t="b">
         <v>0</v>
       </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>SINO GAS HLDGS</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Sino Gas Holdings Group Limited</t>
-        </is>
-      </c>
       <c r="DF2" t="n">
-        <v>9733</v>
+        <v>5.3571377</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.36111107</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>0.72 - 3.0</t>
-        </is>
+        <v>0.59</v>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-2.02</v>
+        <v>1545960600000</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0.6733333500000001</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>27.272724</v>
-      </c>
-      <c r="DM2" t="n">
+        <v>0.029999971</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>0.53 - 0.62</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>122100</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.099999964</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.20408155</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>0.49 - 2.82</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.7907802</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-70.50001</v>
+      </c>
+      <c r="DU2" t="n">
         <v>1743169472</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DV2" t="n">
         <v>1743169472</v>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.044400036</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.047456216</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.03915</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.038414363</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
       </c>
       <c r="DW2" t="b">
         <v>0</v>
       </c>
-      <c r="DX2" t="b">
-        <v>0</v>
+      <c r="DX2" t="n">
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DY2" t="n">
-        <v>1545960600000</v>
+        <v>-0.26820004</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.00999999</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>0.94 - 0.99</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+        <v>-0.3125146</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.40550005</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.40733305</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>15</v>
       </c>
       <c r="ED2" t="n">
-        <v>1780293712</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-1.0101</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.98</v>
+        <v>15</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>Sino Gas Holdings Group Limited</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
       </c>
       <c r="EG2" t="inlineStr"/>
     </row>
